--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="309">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -821,6 +821,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Act.statusCode</t>
@@ -7050,7 +7054,7 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -7058,10 +7062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7087,10 +7091,10 @@
         <v>91</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7121,7 +7125,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7139,7 +7143,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7159,10 +7163,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7260,10 +7264,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7304,7 +7308,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -7363,10 +7367,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7466,10 +7470,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7569,10 +7573,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7672,10 +7676,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7775,10 +7779,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7876,10 +7880,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7977,10 +7981,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8080,10 +8084,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8183,10 +8187,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8286,10 +8290,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8312,7 +8316,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8365,7 +8369,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8385,10 +8389,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8411,7 +8415,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8444,7 +8448,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8462,7 +8466,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8482,10 +8486,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8541,25 +8545,25 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8579,10 +8583,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8605,7 +8609,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8658,7 +8662,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8678,10 +8682,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8704,7 +8708,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8757,7 +8761,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8777,10 +8781,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8803,7 +8807,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8856,7 +8860,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8876,10 +8880,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8902,7 +8906,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8955,7 +8959,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8975,10 +8979,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9001,7 +9005,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9054,7 +9058,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9074,10 +9078,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9100,7 +9104,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9153,7 +9157,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9173,10 +9177,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9199,7 +9203,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9252,7 +9256,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9272,10 +9276,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9298,7 +9302,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9351,7 +9355,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9371,10 +9375,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9397,7 +9401,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9450,7 +9454,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9470,10 +9474,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9496,7 +9500,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9549,7 +9553,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9569,10 +9573,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9595,7 +9599,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9648,7 +9652,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
